--- a/docs/01_db/テーブル定義書.xlsx
+++ b/docs/01_db/テーブル定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CEBB65-0CF8-4038-915E-2D954C19FAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F5DB0F-C0C0-45AB-951A-1DED86DE1D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E487D426-0BB0-4F55-A384-FFACA8F2DE71}"/>
+    <workbookView xWindow="33255" yWindow="585" windowWidth="19215" windowHeight="12975" xr2:uid="{E487D426-0BB0-4F55-A384-FFACA8F2DE71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,33 +39,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
   <si>
     <t>PK</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Id</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Email</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EmpStatus</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FK</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DepId</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -148,10 +128,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ユニーク</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -185,6 +161,47 @@
   </si>
   <si>
     <t>[Department]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータスID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス名</t>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+  </si>
+  <si>
+    <t>[EmpStatus]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>emp_status_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dep_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>email</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -664,46 +681,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30BAE26-FAC3-41F5-B044-92B5725A6410}">
-  <dimension ref="B1:J12"/>
+  <dimension ref="B1:J17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -711,26 +731,26 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -740,15 +760,17 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
     </row>
@@ -759,32 +781,40 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4">
         <v>4</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" s="5" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -796,24 +826,20 @@
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="7"/>
@@ -828,36 +854,36 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -865,26 +891,26 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -894,26 +920,113 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="C15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>21</v>
+      <c r="H17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/01_db/テーブル定義書.xlsx
+++ b/docs/01_db/テーブル定義書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\WEBアプリ開発演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F5DB0F-C0C0-45AB-951A-1DED86DE1D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACD04A8-078E-4B10-B507-A6975D1EFC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33255" yWindow="585" windowWidth="19215" windowHeight="12975" xr2:uid="{E487D426-0BB0-4F55-A384-FFACA8F2DE71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E487D426-0BB0-4F55-A384-FFACA8F2DE71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>PK</t>
     <phoneticPr fontId="1"/>
@@ -124,10 +124,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>INT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ユニーク</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -202,6 +198,13 @@
   </si>
   <si>
     <t>name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>項番</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -694,12 +697,12 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -720,7 +723,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>6</v>
@@ -735,22 +738,22 @@
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -760,13 +763,13 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>8</v>
@@ -781,22 +784,22 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -808,13 +811,13 @@
         <v>8</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -829,13 +832,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -854,7 +857,7 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -880,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>6</v>
@@ -895,22 +898,22 @@
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -920,27 +923,27 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -966,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>6</v>
@@ -981,22 +984,22 @@
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -1006,22 +1009,22 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
